--- a/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
+++ b/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$48</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="379">
   <si>
     <t>Property</t>
   </si>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/AllergyIntolerance</t>
+    <t>http://hl7.eu/fhir/base/StructureDefinition/allergyIntolerance-eu-core</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -350,7 +350,7 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
+    <t>Language of the allergy or intolerance content</t>
   </si>
   <si>
     <t>The base language in which the resource is written.</t>
@@ -426,33 +426,151 @@
     <t>AllergyIntolerance.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.extension:abatement</t>
+  </si>
+  <si>
+    <t>abatement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {allergyintolerance-abatement}
+</t>
+  </si>
+  <si>
+    <t>When the allergy or intolerance resolved</t>
+  </si>
+  <si>
+    <t>The date or estimated date that the allergy or intolerance resolved. This is called abatement because of the many overloaded connotations associated with resolution.</t>
+  </si>
+  <si>
+    <t>Age is generally used when the patient reports an age at which the allergy or intolerance abated. If there is no abatement element, the clinicalStatus can be used to convey whether allergy or intolerance has resolved or not. When abatementString exists, it conveys that the allergy or intolerance is abated.</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.extension:abatement.id</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.extension.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.extension:abatement.extension</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.extension.extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.extension:abatement.url</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/allergyintolerance-abatement</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.extension:abatement.value[x]</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.extension.value[x]</t>
+  </si>
+  <si>
+    <t>dateTime
+AgePeriodRangestring</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.extension:abatement.value[x]:valueDateTime</t>
+  </si>
+  <si>
+    <t>valueDateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>End date</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -460,6 +578,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -473,7 +594,7 @@
 </t>
   </si>
   <si>
-    <t>External ids for this item</t>
+    <t>Business identifier for the allergy or intolerance</t>
   </si>
   <si>
     <t>Business identifiers assigned to this AllergyIntolerance by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
@@ -501,7 +622,7 @@
 </t>
   </si>
   <si>
-    <t>active | inactive | resolved</t>
+    <t>Current allergy or Intolerance status</t>
   </si>
   <si>
     <t>The clinical status of the allergy or intolerance.</t>
@@ -530,7 +651,7 @@
     <t>AllergyIntolerance.verificationStatus</t>
   </si>
   <si>
-    <t>unconfirmed | confirmed | refuted | entered-in-error</t>
+    <t>Certainty</t>
   </si>
   <si>
     <t>Assertion about certainty associated with the propensity, or potential risk, of a reaction to the identified substance (including pharmaceutical product).</t>
@@ -555,7 +676,7 @@
 Class</t>
   </si>
   <si>
-    <t>allergy | intolerance - Underlying mechanism (if known)</t>
+    <t>Type of propensity</t>
   </si>
   <si>
     <t>Identification of the underlying physiological mechanism for the reaction risk.</t>
@@ -614,7 +735,7 @@
 SeriousnessContra-indicationRisk</t>
   </si>
   <si>
-    <t>low | high | unable-to-assess</t>
+    <t>Criticality</t>
   </si>
   <si>
     <t>Estimate of the potential clinical harm, or seriousness, of the reaction to the identified substance.</t>
@@ -658,13 +779,10 @@
 The 'substanceExposureRisk' extension is available as a structured and more flexible alternative to the 'code' element for making positive or negative allergy or intolerance statements.  This extension provides the capability to make "no known allergy" (or "no risk of adverse reaction") statements regarding any coded substance/product (including cases when a pre-coordinated "no allergy to x" concept for that substance/product does not exist).  If the 'substanceExposureRisk' extension is present, the AllergyIntolerance.code element SHALL be omitted.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Type of the substance/product, allergy or intolerance condition, or negation/exclusion codes for reporting no known allergies.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/allergyintolerance-code|4.0.1</t>
+    <t>Type of the substance/product, allergy or intolerance condition or a code for absent/unknown allergy.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/allergies-intolerances-uv-ips</t>
   </si>
   <si>
     <t>substance/product:@@ -697,7 +815,7 @@
 </t>
   </si>
   <si>
-    <t>Who the sensitivity is for</t>
+    <t>Who the allergy or intolerance concerns</t>
   </si>
   <si>
     <t>The patient who has the allergy or intolerance.</t>
@@ -734,11 +852,7 @@
     <t>AllergyIntolerance.onset[x]</t>
   </si>
   <si>
-    <t>dateTime
-AgePeriodRangestring</t>
-  </si>
-  <si>
-    <t>When allergy or intolerance was identified</t>
+    <t>Date of onset of the allergy or intolerance</t>
   </si>
   <si>
     <t>Estimated or actual date,  date-time, or age when allergy or intolerance was identified.</t>
@@ -750,14 +864,19 @@
     <t>FiveWs.init</t>
   </si>
   <si>
+    <t>AllergyIntolerance.onset[x]:onsetDateTime</t>
+  </si>
+  <si>
+    <t>onsetDateTime</t>
+  </si>
+  <si>
+    <t>Onset date</t>
+  </si>
+  <si>
     <t>AllergyIntolerance.recordedDate</t>
   </si>
   <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Date first version of the resource instance was recorded</t>
+    <t>Date when the allergy or intolerance was recorded</t>
   </si>
   <si>
     <t>The recordedDate represents when this particular AllergyIntolerance record was created in the system, which is often a system-generated date.</t>
@@ -783,7 +902,7 @@
 </t>
   </si>
   <si>
-    <t>Who recorded the sensitivity</t>
+    <t>Who recorded the allergy or intolerance</t>
   </si>
   <si>
     <t>Individual who recorded the record and takes responsibility for its content.</t>
@@ -806,7 +925,7 @@
 </t>
   </si>
   <si>
-    <t>Source of the information about the allergy</t>
+    <t>Who asserts the allergy or intolerance</t>
   </si>
   <si>
     <t>The source of the information about the allergy that is recorded.</t>
@@ -858,6 +977,78 @@
     <t>subjectOf.observationEvent[code="annotation"].value</t>
   </si>
   <si>
+    <t>AllergyIntolerance.note.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.note.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.note.author[x]</t>
+  </si>
+  <si>
+    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
+string</t>
+  </si>
+  <si>
+    <t>Individual responsible for the annotation</t>
+  </si>
+  <si>
+    <t>The individual responsible for making the annotation.</t>
+  </si>
+  <si>
+    <t>Organization is used when there's no need for specific attribution as to who made the comment.</t>
+  </si>
+  <si>
+    <t>Annotation.author[x]</t>
+  </si>
+  <si>
+    <t>Act.participant[typeCode=AUT].role</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.note.time</t>
+  </si>
+  <si>
+    <t>When the annotation was made</t>
+  </si>
+  <si>
+    <t>Indicates when this particular annotation was made.</t>
+  </si>
+  <si>
+    <t>Annotation.time</t>
+  </si>
+  <si>
+    <t>Act.effectiveTime</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.note.text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">markdown
+</t>
+  </si>
+  <si>
+    <t>Additional information about the allergy or intolerance</t>
+  </si>
+  <si>
+    <t>The text of the annotation in markdown format.</t>
+  </si>
+  <si>
+    <t>Annotation.text</t>
+  </si>
+  <si>
+    <t>Act.text</t>
+  </si>
+  <si>
     <t>AllergyIntolerance.reaction</t>
   </si>
   <si>
@@ -877,29 +1068,7 @@
     <t>AllergyIntolerance.reaction.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>AllergyIntolerance.reaction.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>AllergyIntolerance.reaction.modifierExtension</t>
@@ -931,10 +1100,10 @@
     <t>Coding of the specific substance (or pharmaceutical product) with a terminology capable of triggering decision support should be used wherever possible.  The 'code' element allows for the use of a specific substance or pharmaceutical product, or a group or class of substances. In the case of an allergy or intolerance to a class of substances, (for example, "penicillins"), the 'reaction.substance' element could be used to code the specific substance that was identified as having caused the reaction (for example, "amoxycillin"). Duplication of the value in the 'code' and 'reaction.substance' elements is acceptable when a specific substance has been recorded in 'code'.</t>
   </si>
   <si>
-    <t>Codes defining the type of the substance (including pharmaceutical products).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/substance-code|4.0.1</t>
+    <t>example</t>
+  </si>
+  <si>
+    <t>http://terminology.ehdsi.eu/ValueSet/eHDSIAllergenNoDrug</t>
   </si>
   <si>
     <t>outBoundRelationship[typeCode=SAS].target[classCode=SBADM, code &lt;= ExposureCode].participation[typeCode=CSM].role[classCode=ADMM].player[classCode=MAT, determinerCode=KIND, code &lt;= ExposureAgentEntityType]</t>
@@ -956,10 +1125,10 @@
     <t>Manifestation can be expressed as a single word, phrase or brief description. For example: nausea, rash or no reaction. It is preferable that manifestation should be coded with a terminology, where possible. The values entered here may be used to display on an application screen as part of a list of adverse reactions, as recommended in the UK NHS CUI guidelines.  Terminologies commonly used include, but are not limited to, SNOMED CT or ICD10.</t>
   </si>
   <si>
-    <t>Clinical symptoms and/or signs that are observed or associated with an Adverse Reaction Event.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
+    <t>Type of allergy or intolerance reaction expected to be used in MyHealth@EU</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/allergy-reaction-uv-ips</t>
   </si>
   <si>
     <t>AL1-5</t>
@@ -987,7 +1156,7 @@
     <t>AllergyIntolerance.reaction.onset</t>
   </si>
   <si>
-    <t>Date(/time) when manifestations showed</t>
+    <t>Reaction onset</t>
   </si>
   <si>
     <t>Record of the date and/or time of the onset of the Reaction.</t>
@@ -999,7 +1168,7 @@
     <t>AllergyIntolerance.reaction.severity</t>
   </si>
   <si>
-    <t>mild | moderate | severe (of event as a whole)</t>
+    <t>Reaction severity</t>
   </si>
   <si>
     <t>Clinical assessment of the severity of the reaction event as a whole, potentially considering multiple different manifestations.</t>
@@ -1361,12 +1530,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM36"/>
+  <dimension ref="A1:AM48"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="36.9609375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="52.0234375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="36.9609375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.90625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1392,7 +1561,7 @@
     <col min="26" max="26" width="50.62109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="34.6328125" customWidth="true" bestFit="true" hidden="true"/>
@@ -2307,7 +2476,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2326,17 +2495,15 @@
         <v>79</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>136</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>79</v>
@@ -2373,16 +2540,14 @@
         <v>79</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>137</v>
@@ -2400,7 +2565,7 @@
         <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>79</v>
@@ -2414,43 +2579,43 @@
         <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>79</v>
       </c>
@@ -2498,7 +2663,7 @@
         <v>79</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2513,7 +2678,7 @@
         <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>79</v>
@@ -2524,10 +2689,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2538,7 +2703,7 @@
         <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>79</v>
@@ -2547,23 +2712,19 @@
         <v>79</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>89</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="O11" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>79</v>
       </c>
@@ -2611,33 +2772,33 @@
         <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="AM11" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" hidden="true">
+      <c r="A12" t="s" s="2">
         <v>152</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>153</v>
@@ -2651,29 +2812,27 @@
         <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>79</v>
@@ -2698,60 +2857,60 @@
         <v>79</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="Y12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" hidden="true">
+      <c r="A13" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="Z12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK12" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2759,31 +2918,31 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>154</v>
+        <v>101</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2791,7 +2950,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>79</v>
@@ -2809,13 +2968,13 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>167</v>
+        <v>79</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -2833,25 +2992,25 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>87</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>160</v>
+        <v>79</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>169</v>
+        <v>130</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>162</v>
+        <v>79</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>79</v>
@@ -2859,18 +3018,18 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>171</v>
+        <v>79</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>87</v>
@@ -2882,20 +3041,18 @@
         <v>79</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>107</v>
+        <v>165</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>79</v>
@@ -2920,71 +3077,71 @@
         <v>79</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>175</v>
+        <v>79</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>176</v>
+        <v>79</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="AF14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI14" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>177</v>
+        <v>130</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>178</v>
+        <v>79</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>179</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="D15" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>79</v>
@@ -2993,20 +3150,18 @@
         <v>79</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>79</v>
@@ -3031,13 +3186,13 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>79</v>
@@ -3055,70 +3210,72 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>79</v>
+        <v>170</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>187</v>
+        <v>130</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>178</v>
+        <v>79</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>188</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>79</v>
       </c>
@@ -3142,13 +3299,13 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>194</v>
+        <v>79</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>195</v>
+        <v>79</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>79</v>
@@ -3166,50 +3323,50 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>196</v>
+        <v>130</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>198</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>79</v>
@@ -3218,18 +3375,20 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>79</v>
       </c>
@@ -3253,13 +3412,13 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>206</v>
+        <v>79</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
@@ -3277,13 +3436,13 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>79</v>
@@ -3292,52 +3451,54 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>209</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>211</v>
+        <v>79</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>79</v>
@@ -3362,13 +3523,13 @@
         <v>79</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>79</v>
+        <v>196</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>79</v>
+        <v>194</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>79</v>
@@ -3386,36 +3547,36 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>79</v>
+        <v>198</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>217</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3429,24 +3590,26 @@
         <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -3471,13 +3634,13 @@
         <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>79</v>
+        <v>196</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>79</v>
@@ -3495,7 +3658,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3504,16 +3667,16 @@
         <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>79</v>
+        <v>198</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -3521,14 +3684,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3544,18 +3707,20 @@
         <v>79</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>225</v>
+        <v>107</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -3580,13 +3745,13 @@
         <v>79</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>79</v>
+        <v>196</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>79</v>
+        <v>213</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>79</v>
+        <v>214</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>79</v>
@@ -3604,7 +3769,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3619,32 +3784,32 @@
         <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>79</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>79</v>
@@ -3653,18 +3818,20 @@
         <v>79</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>231</v>
+        <v>107</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -3689,13 +3856,13 @@
         <v>79</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>79</v>
+        <v>196</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>79</v>
+        <v>223</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>79</v>
+        <v>224</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>79</v>
@@ -3713,13 +3880,13 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>79</v>
@@ -3728,25 +3895,25 @@
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>236</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3762,18 +3929,20 @@
         <v>79</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>239</v>
+        <v>107</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>79</v>
@@ -3798,13 +3967,13 @@
         <v>79</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>79</v>
+        <v>196</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>79</v>
+        <v>233</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>79</v>
@@ -3822,7 +3991,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3837,35 +4006,35 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>79</v>
+        <v>236</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>79</v>
@@ -3874,16 +4043,16 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>246</v>
+        <v>192</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3909,13 +4078,13 @@
         <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>79</v>
+        <v>242</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>79</v>
+        <v>243</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>79</v>
@@ -3933,7 +4102,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -3948,29 +4117,29 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>79</v>
+        <v>248</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>87</v>
@@ -3982,20 +4151,18 @@
         <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -4044,10 +4211,10 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>87</v>
@@ -4059,21 +4226,21 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>79</v>
+        <v>253</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>79</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4084,7 +4251,7 @@
         <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>79</v>
@@ -4096,17 +4263,15 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -4155,13 +4320,13 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>79</v>
@@ -4170,10 +4335,10 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>79</v>
+        <v>260</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
@@ -4181,10 +4346,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4195,7 +4360,7 @@
         <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>79</v>
@@ -4207,13 +4372,13 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>265</v>
+        <v>165</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4252,25 +4417,23 @@
         <v>79</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>79</v>
@@ -4279,10 +4442,10 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>79</v>
+        <v>265</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
@@ -4290,12 +4453,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>79</v>
       </c>
@@ -4316,13 +4481,13 @@
         <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>270</v>
+        <v>173</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4373,7 +4538,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4385,13 +4550,13 @@
         <v>79</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>79</v>
+        <v>265</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
@@ -4399,21 +4564,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>79</v>
@@ -4425,17 +4590,15 @@
         <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>134</v>
+        <v>270</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -4484,72 +4647,68 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>133</v>
+        <v>277</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>79</v>
       </c>
@@ -4597,40 +4756,40 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" hidden="true">
+      <c r="A30" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AG29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>283</v>
-      </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4640,25 +4799,25 @@
         <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J30" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K30" t="s" s="2">
-        <v>154</v>
+        <v>284</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4684,13 +4843,13 @@
         <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>287</v>
+        <v>79</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>79</v>
@@ -4708,7 +4867,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4723,32 +4882,32 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AL30" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AM30" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>291</v>
+        <v>79</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>79</v>
@@ -4760,7 +4919,7 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>292</v>
@@ -4795,13 +4954,13 @@
         <v>79</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>295</v>
+        <v>79</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>296</v>
+        <v>79</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>79</v>
@@ -4819,13 +4978,13 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>79</v>
@@ -4834,32 +4993,32 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>177</v>
+        <v>295</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>297</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>299</v>
+        <v>79</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>79</v>
@@ -4871,16 +5030,16 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>270</v>
+        <v>297</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4930,13 +5089,13 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>79</v>
@@ -4945,7 +5104,7 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>79</v>
@@ -4956,10 +5115,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4982,13 +5141,13 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>231</v>
+        <v>303</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>305</v>
+        <v>147</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>306</v>
+        <v>148</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5039,7 +5198,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>304</v>
+        <v>149</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5051,35 +5210,35 @@
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>228</v>
+        <v>151</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>307</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>79</v>
@@ -5091,16 +5250,16 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>311</v>
+        <v>179</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5126,46 +5285,46 @@
         <v>79</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>312</v>
+        <v>79</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>313</v>
+        <v>79</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>308</v>
+        <v>155</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>196</v>
+        <v>151</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>79</v>
@@ -5176,10 +5335,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5199,19 +5358,19 @@
         <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>154</v>
+        <v>308</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5237,13 +5396,13 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>318</v>
+        <v>79</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>319</v>
+        <v>79</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>79</v>
@@ -5261,7 +5420,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5276,21 +5435,21 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>79</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5301,7 +5460,7 @@
         <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>79</v>
@@ -5310,20 +5469,18 @@
         <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>259</v>
+        <v>173</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -5372,13 +5529,13 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>79</v>
@@ -5387,17 +5544,1341 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>263</v>
+        <v>318</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="37" hidden="true">
+      <c r="A37" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" hidden="true">
+      <c r="A39" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="P41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="Y42" s="2"/>
+      <c r="Z42" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM36">
+  <autoFilter ref="A1:AM48">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5407,7 +6888,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI35">
+  <conditionalFormatting sqref="A2:AI47">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
+++ b/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1706" uniqueCount="380">
   <si>
     <t>Property</t>
   </si>
@@ -811,7 +811,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.no/fhir/ig/demo-at/StructureDefinition/demo-at-patient)
+    <t xml:space="preserve">Reference(http://hl7.eu/fhir/base/StructureDefinition/patient-eu-core)
 </t>
   </si>
   <si>
@@ -876,10 +876,13 @@
     <t>AllergyIntolerance.recordedDate</t>
   </si>
   <si>
-    <t>Date when the allergy or intolerance was recorded</t>
-  </si>
-  <si>
-    <t>The recordedDate represents when this particular AllergyIntolerance record was created in the system, which is often a system-generated date.</t>
+    <t>Registreringsdato</t>
+  </si>
+  <si>
+    <t>Dato for registrering av allergi eller intoleranse</t>
+  </si>
+  <si>
+    <t>Obligatorisk i Kjernejournal</t>
   </si>
   <si>
     <t>.participation[typeCode=AUT].time</t>
@@ -1119,7 +1122,7 @@
     <t>Clinical symptoms/signs associated with the Event</t>
   </si>
   <si>
-    <t>Clinical symptoms and/or signs that are observed or associated with the adverse reaction event.</t>
+    <t>Eksempel på kommentar/tillegg i norsk utgave</t>
   </si>
   <si>
     <t>Manifestation can be expressed as a single word, phrase or brief description. For example: nausea, rash or no reaction. It is preferable that manifestation should be coded with a terminology, where possible. The values entered here may be used to display on an application screen as part of a list of adverse reactions, as recommended in the UK NHS CUI guidelines.  Terminologies commonly used include, but are not limited to, SNOMED CT or ICD10.</t>
@@ -3460,7 +3463,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>191</v>
       </c>
@@ -3479,7 +3482,7 @@
         <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>88</v>
@@ -3571,7 +3574,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>201</v>
       </c>
@@ -3590,7 +3593,7 @@
         <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>88</v>
@@ -4015,7 +4018,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>237</v>
       </c>
@@ -4034,7 +4037,7 @@
         <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>79</v>
@@ -4575,7 +4578,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>87</v>
@@ -4598,7 +4601,9 @@
       <c r="M28" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="N28" s="2"/>
+      <c r="N28" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -4662,25 +4667,25 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4699,13 +4704,13 @@
         <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4756,7 +4761,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4771,10 +4776,10 @@
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>79</v>
@@ -4782,14 +4787,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4808,16 +4813,16 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4867,7 +4872,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4882,21 +4887,21 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4922,13 +4927,13 @@
         <v>173</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4978,7 +4983,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -4993,7 +4998,7 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>79</v>
@@ -5004,10 +5009,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5030,16 +5035,16 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5089,7 +5094,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5104,7 +5109,7 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>79</v>
@@ -5115,10 +5120,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5141,7 +5146,7 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>147</v>
@@ -5224,10 +5229,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5253,10 +5258,10 @@
         <v>132</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>179</v>
@@ -5335,10 +5340,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5361,16 +5366,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5420,7 +5425,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5435,7 +5440,7 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>79</v>
@@ -5446,10 +5451,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5475,10 +5480,10 @@
         <v>173</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5529,7 +5534,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5544,7 +5549,7 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>79</v>
@@ -5555,10 +5560,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5581,13 +5586,13 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5638,7 +5643,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>87</v>
@@ -5653,7 +5658,7 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>79</v>
@@ -5664,10 +5669,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5690,13 +5695,13 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5747,7 +5752,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5762,7 +5767,7 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>79</v>
@@ -5773,10 +5778,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5799,7 +5804,7 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>147</v>
@@ -5882,10 +5887,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5911,10 +5916,10 @@
         <v>132</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>179</v>
@@ -5993,14 +5998,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6022,10 +6027,10 @@
         <v>132</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>179</v>
@@ -6080,7 +6085,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6106,10 +6111,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6135,13 +6140,13 @@
         <v>192</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6167,11 +6172,11 @@
         <v>79</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>79</v>
@@ -6189,7 +6194,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6204,7 +6209,7 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>79</v>
@@ -6215,14 +6220,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6244,13 +6249,13 @@
         <v>192</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6279,10 +6284,10 @@
         <v>111</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -6300,7 +6305,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>87</v>
@@ -6321,19 +6326,19 @@
         <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6352,16 +6357,16 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6411,7 +6416,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6426,7 +6431,7 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>79</v>
@@ -6437,10 +6442,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6466,10 +6471,10 @@
         <v>173</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6520,7 +6525,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6541,15 +6546,15 @@
         <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6575,13 +6580,13 @@
         <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6610,10 +6615,10 @@
         <v>196</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>79</v>
@@ -6631,7 +6636,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6657,10 +6662,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6686,13 +6691,13 @@
         <v>192</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6718,13 +6723,13 @@
         <v>79</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>79</v>
@@ -6742,7 +6747,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6757,7 +6762,7 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>79</v>
@@ -6768,10 +6773,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6794,16 +6799,16 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6853,7 +6858,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6868,7 +6873,7 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>79</v>

--- a/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
+++ b/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,13 +66,13 @@
     <t>Publisher</t>
   </si>
   <si>
-    <t>HL7 Norge</t>
+    <t>Helsedirektoratet</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>HL7 Norge (https://www.hl7.no)</t>
+    <t>Helsedirektoratet (https://www.helsedirektoratet.no)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -4601,10 +4601,10 @@
       <c r="M28" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="N28" s="2"/>
+      <c r="O28" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
       </c>

--- a/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
+++ b/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1706" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="379">
   <si>
     <t>Property</t>
   </si>
@@ -779,10 +779,7 @@
 The 'substanceExposureRisk' extension is available as a structured and more flexible alternative to the 'code' element for making positive or negative allergy or intolerance statements.  This extension provides the capability to make "no known allergy" (or "no risk of adverse reaction") statements regarding any coded substance/product (including cases when a pre-coordinated "no allergy to x" concept for that substance/product does not exist).  If the 'substanceExposureRisk' extension is present, the AllergyIntolerance.code element SHALL be omitted.</t>
   </si>
   <si>
-    <t>Type of the substance/product, allergy or intolerance condition or a code for absent/unknown allergy.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/allergies-intolerances-uv-ips</t>
+    <t>http://hl7.no/fhir/ig/demo-at/ValueSet/annen-allergi-som-kritisk-informasjon-7514</t>
   </si>
   <si>
     <t>substance/product:@@ -1561,7 +1558,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="106.67578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.62109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.96484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -4083,11 +4080,9 @@
       <c r="X23" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="Y23" t="s" s="2">
+      <c r="Y23" s="2"/>
+      <c r="Z23" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>79</v>
@@ -4120,25 +4115,25 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>246</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4157,13 +4152,13 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4214,7 +4209,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>87</v>
@@ -4229,21 +4224,21 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>254</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4266,13 +4261,13 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4323,7 +4318,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4338,10 +4333,10 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
@@ -4349,10 +4344,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4378,10 +4373,10 @@
         <v>165</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4430,7 +4425,7 @@
         <v>136</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4445,10 +4440,10 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
@@ -4456,13 +4451,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="C27" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>79</v>
@@ -4487,10 +4482,10 @@
         <v>173</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4541,7 +4536,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4556,10 +4551,10 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
@@ -4567,10 +4562,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4596,14 +4591,14 @@
         <v>173</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -4652,7 +4647,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4667,25 +4662,25 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>275</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4704,13 +4699,13 @@
         <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4761,7 +4756,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4776,10 +4771,10 @@
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>79</v>
@@ -4787,14 +4782,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4813,16 +4808,16 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4872,7 +4867,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4887,21 +4882,21 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>291</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4927,13 +4922,13 @@
         <v>173</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4983,7 +4978,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -4998,7 +4993,7 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>79</v>
@@ -5009,10 +5004,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5035,16 +5030,16 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5094,7 +5089,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5109,7 +5104,7 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>79</v>
@@ -5120,10 +5115,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5146,7 +5141,7 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>147</v>
@@ -5229,10 +5224,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5258,10 +5253,10 @@
         <v>132</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>179</v>
@@ -5340,10 +5335,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5366,16 +5361,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5425,7 +5420,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5440,7 +5435,7 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>79</v>
@@ -5451,10 +5446,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5480,10 +5475,10 @@
         <v>173</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5534,7 +5529,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5549,7 +5544,7 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>79</v>
@@ -5560,10 +5555,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5586,13 +5581,13 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5643,7 +5638,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>87</v>
@@ -5658,7 +5653,7 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>79</v>
@@ -5669,10 +5664,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5695,13 +5690,13 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5752,7 +5747,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5767,7 +5762,7 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>79</v>
@@ -5778,10 +5773,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5804,7 +5799,7 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>147</v>
@@ -5887,10 +5882,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5916,10 +5911,10 @@
         <v>132</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>179</v>
@@ -5998,14 +5993,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6027,10 +6022,10 @@
         <v>132</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>179</v>
@@ -6085,7 +6080,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6111,10 +6106,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6140,13 +6135,13 @@
         <v>192</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6172,11 +6167,11 @@
         <v>79</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>79</v>
@@ -6194,7 +6189,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6209,7 +6204,7 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>79</v>
@@ -6220,14 +6215,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6249,13 +6244,13 @@
         <v>192</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6284,11 +6279,11 @@
         <v>111</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="Z43" t="s" s="2">
-        <v>351</v>
-      </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
       </c>
@@ -6305,7 +6300,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>87</v>
@@ -6326,19 +6321,19 @@
         <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6357,16 +6352,16 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6416,7 +6411,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6431,7 +6426,7 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>79</v>
@@ -6442,10 +6437,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6471,10 +6466,10 @@
         <v>173</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6525,7 +6520,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6540,21 +6535,21 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6580,13 +6575,13 @@
         <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6615,11 +6610,11 @@
         <v>196</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>368</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>79</v>
       </c>
@@ -6636,7 +6631,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6662,10 +6657,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6691,13 +6686,13 @@
         <v>192</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6723,14 +6718,14 @@
         <v>79</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>374</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>79</v>
       </c>
@@ -6747,7 +6742,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6762,7 +6757,7 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>79</v>
@@ -6773,10 +6768,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6799,16 +6794,16 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6858,7 +6853,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6873,7 +6868,7 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>79</v>

--- a/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
+++ b/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$48</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1706" uniqueCount="380">
   <si>
     <t>Property</t>
   </si>
@@ -57,6 +54,9 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil for registrering av allergi og intoleranse i demo-IG.</t>
+    <t>Dummy-tekst: Helse-NIM for overfølsomhet er en liste som inneholder informasjon om unormale reaksjoner, symptomer eller funn initiert av eksponering for en definert stimulus i en dose som normalt tolereres av andre. Informasjon om en pasients overfølsomhet er relevant i mange situasjoner, som ved vaksinasjon, kost på institusjon, rekvirering og utlevering av legemidler, herunder inkludert muligheten til å dele informasjon om en avkreftet overfølsomhet.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -769,17 +769,13 @@
     <t>Code that identifies the allergy or intolerance</t>
   </si>
   <si>
-    <t>Code for an allergy or intolerance statement (either a positive or a negated/excluded statement).  This may be a code for a substance or pharmaceutical product that is considered to be responsible for the adverse reaction risk (e.g., "Latex"), an allergy or intolerance condition (e.g., "Latex allergy"), or a negated/excluded code for a specific substance or class (e.g., "No latex allergy") or a general or categorical negated statement (e.g.,  "No known allergy", "No known drug allergies").  Note: the substance for a specific reaction may be different from the substance identified as the cause of the risk, but it must be consistent with it. For instance, it may be a more specific substance (e.g. a brand medication) or a composite product that includes the identified substance. It must be clinically safe to only process the 'code' and ignore the 'reaction.substance'.  If a receiving system is unable to confirm that AllergyIntolerance.reaction.substance falls within the semantic scope of AllergyIntolerance.code, then the receiving system should ignore AllergyIntolerance.reaction.substance.</t>
-  </si>
-  <si>
-    <t>It is strongly recommended that this element be populated using a terminology, where possible. For example, some terminologies used include RxNorm, SNOMED CT, DM+D, NDFRT, ICD-9, IDC-10, UNII, and ATC. Plain text should only be used if there is no appropriate terminology available. Additional details can be specified in the text.--When a substance or product code is specified for the 'code' element, the "default" semantic context is that this is a positive statement of an allergy or intolerance (depending on the value of the 'type' element, if present) condition to the specified substance/product.  In the corresponding SNOMED CT allergy model, the specified substance/product is the target (destination) of the "Causative agent" relationship.--The 'substanceExposureRisk' extension is available as a structured and more flexible alternative to the 'code' element for making positive or negative allergy or intolerance statements.  This extension provides the capability to make "no known allergy" (or "no risk of adverse reaction") statements regarding any coded substance/product (including cases when a pre-coordinated "no allergy to x" concept for that substance/product does not exist).  If the 'substanceExposureRisk' extension is present, the AllergyIntolerance.code element SHALL be omitted.</t>
-  </si>
-  <si>
-    <t>http://hl7.no/fhir/ig/demo-at/ValueSet/annen-allergi-som-kritisk-informasjon-7514</t>
+    <t>Hvilke agens (substans, trigger, materiale) som kan knyttes til overfølsomheten.</t>
+  </si>
+  <si>
+    <t>Merk: Det vil bli endringer i anbefaling til koding av legemidler og substanser (agens) når ny standard for identifisering av legemidler implementeres i Norge (IDMP).</t>
+  </si>
+  <si>
+    <t>http://hl7.no/fhir/ig/demo-at/ValueSet/allergener-7852</t>
   </si>
   <si>
     <t>substance/product:@@ -876,7 +872,7 @@
     <t>Registreringsdato</t>
   </si>
   <si>
-    <t>Dato for registrering av allergi eller intoleranse</t>
+    <t xml:space="preserve">Tidspunkt da overfølsomheten eller den uønskede reaksjonen ble konstatert. Tidspunkt kan være spesifikk (dag-tidspunkt) eller uspesifikk (årstall, tiår). </t>
   </si>
   <si>
     <t>Obligatorisk i Kjernejournal</t>
@@ -968,7 +964,7 @@
     <t>Additional text not captured in other fields</t>
   </si>
   <si>
-    <t>Additional narrative about the propensity for the Adverse Reaction, not captured in other fields.</t>
+    <t>Kommentar eller supplerende opplysninger.</t>
   </si>
   <si>
     <t>For example: including reason for flagging a seriousness of 'High Risk'; and instructions related to future exposure or administration of the substance, such as administration within an Intensive Care Unit or under corticosteroid cover. The notes should be related to an allergy or intolerance as a condition in general and not related to any particular episode of it. For episode notes and descriptions, use AllergyIntolerance.event.description and  AllergyIntolerance.event.notes.</t>
@@ -1119,7 +1115,7 @@
     <t>Clinical symptoms/signs associated with the Event</t>
   </si>
   <si>
-    <t>Eksempel på kommentar/tillegg i norsk utgave</t>
+    <t>Clinical symptoms and/or signs that are observed or associated with the adverse reaction event.</t>
   </si>
   <si>
     <t>Manifestation can be expressed as a single word, phrase or brief description. For example: nausea, rash or no reaction. It is preferable that manifestation should be coded with a terminology, where possible. The values entered here may be used to display on an application screen as part of a list of adverse reactions, as recommended in the UK NHS CUI guidelines.  Terminologies commonly used include, but are not limited to, SNOMED CT or ICD10.</t>
@@ -1342,21 +1338,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1421,106 +1402,108 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1558,7 +1541,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="106.67578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="64.96484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.62109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -1575,5327 +1558,5309 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="AG2" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH2" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="AG2" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH2" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH8" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH9" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AE9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AG9" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF10" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH10" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AG10" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH10" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH12" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH16" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH17" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AA19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AG19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>200</v>
-      </c>
       <c r="AM19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH21" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH32" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH34" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH38" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH40" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH41" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH43" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH48" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM48">
-    <filterColumn colId="7">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="27">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI47">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
+++ b/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -775,7 +775,7 @@
     <t>Merk: Det vil bli endringer i anbefaling til koding av legemidler og substanser (agens) når ny standard for identifisering av legemidler implementeres i Norge (IDMP).</t>
   </si>
   <si>
-    <t>http://hl7.no/fhir/ig/demo-at/ValueSet/allergener-7852</t>
+    <t>http://hl7.no/fhir/ig/demo-at/ValueSet/annen-allergi-som-kritisk-informasjon-7514</t>
   </si>
   <si>
     <t>substance/product:@@ -1541,7 +1541,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="106.67578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.62109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.96484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
+++ b/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$48</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1706" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="383">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.1.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -851,6 +854,9 @@
     <t>Estimated or actual date,  date-time, or age when allergy or intolerance was identified.</t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>effectiveTime.low</t>
   </si>
   <si>
@@ -863,7 +869,13 @@
     <t>onsetDateTime</t>
   </si>
   <si>
-    <t>Onset date</t>
+    <t>Starttidspunkt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tidspunkt da overfølsomheten eller den uønskede reaksjonen ble konstatert. Tidspunkt kan være spesifikk (dag-tidspunkt) eller uspesifikk (årstall, tiår). </t>
+  </si>
+  <si>
+    <t>EHDS krever dato/tid, alder må konverteres.</t>
   </si>
   <si>
     <t>AllergyIntolerance.recordedDate</t>
@@ -872,7 +884,7 @@
     <t>Registreringsdato</t>
   </si>
   <si>
-    <t xml:space="preserve">Tidspunkt da overfølsomheten eller den uønskede reaksjonen ble konstatert. Tidspunkt kan være spesifikk (dag-tidspunkt) eller uspesifikk (årstall, tiår). </t>
+    <t>The recordedDate represents when this particular AllergyIntolerance record was created in the system, which is often a system-generated date.</t>
   </si>
   <si>
     <t>Obligatorisk i Kjernejournal</t>
@@ -1338,6 +1350,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1675,7 +1702,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -1786,7 +1813,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -1897,7 +1924,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -2006,7 +2033,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>101</v>
       </c>
@@ -2117,7 +2144,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>107</v>
       </c>
@@ -2228,7 +2255,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -2339,7 +2366,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -2450,7 +2477,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -2557,7 +2584,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -2670,7 +2697,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>146</v>
       </c>
@@ -2779,7 +2806,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>153</v>
       </c>
@@ -2888,7 +2915,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>157</v>
       </c>
@@ -2999,7 +3026,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>164</v>
       </c>
@@ -3106,7 +3133,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>172</v>
       </c>
@@ -3217,7 +3244,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>176</v>
       </c>
@@ -3330,7 +3357,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>183</v>
       </c>
@@ -3462,7 +3489,7 @@
         <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>89</v>
@@ -3573,7 +3600,7 @@
         <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>89</v>
@@ -3665,7 +3692,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>209</v>
       </c>
@@ -3776,7 +3803,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>219</v>
       </c>
@@ -3887,7 +3914,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>228</v>
       </c>
@@ -4017,7 +4044,7 @@
         <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>80</v>
@@ -4107,7 +4134,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>247</v>
       </c>
@@ -4216,7 +4243,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>255</v>
       </c>
@@ -4325,7 +4352,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>261</v>
       </c>
@@ -4405,7 +4432,7 @@
         <v>80</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>137</v>
+        <v>264</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>261</v>
@@ -4423,24 +4450,24 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>261</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>80</v>
@@ -4465,13 +4492,15 @@
         <v>174</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
       </c>
@@ -4534,21 +4563,21 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4574,14 +4603,14 @@
         <v>174</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -4630,7 +4659,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4645,25 +4674,25 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4682,13 +4711,13 @@
         <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4739,7 +4768,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4754,25 +4783,25 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4791,16 +4820,16 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4850,7 +4879,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4865,21 +4894,21 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4905,13 +4934,13 @@
         <v>174</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4961,7 +4990,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4976,7 +5005,7 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>80</v>
@@ -4985,12 +5014,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5013,16 +5042,16 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5072,7 +5101,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5087,7 +5116,7 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>80</v>
@@ -5096,12 +5125,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5124,7 +5153,7 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>148</v>
@@ -5205,12 +5234,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5236,10 +5265,10 @@
         <v>133</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>180</v>
@@ -5316,12 +5345,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5344,16 +5373,16 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5403,7 +5432,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5418,7 +5447,7 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>80</v>
@@ -5427,12 +5456,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5458,10 +5487,10 @@
         <v>174</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5512,7 +5541,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5527,7 +5556,7 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>80</v>
@@ -5536,12 +5565,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5564,13 +5593,13 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5621,7 +5650,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>88</v>
@@ -5636,7 +5665,7 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>80</v>
@@ -5645,12 +5674,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5673,13 +5702,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5730,7 +5759,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5745,7 +5774,7 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>80</v>
@@ -5754,12 +5783,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5782,7 +5811,7 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>148</v>
@@ -5863,12 +5892,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5894,10 +5923,10 @@
         <v>133</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>180</v>
@@ -5974,16 +6003,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6005,10 +6034,10 @@
         <v>133</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>180</v>
@@ -6063,7 +6092,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6087,12 +6116,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6118,13 +6147,13 @@
         <v>193</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6150,11 +6179,11 @@
         <v>80</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>80</v>
@@ -6172,7 +6201,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6187,7 +6216,7 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>80</v>
@@ -6196,16 +6225,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6227,13 +6256,13 @@
         <v>193</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6262,10 +6291,10 @@
         <v>112</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>80</v>
@@ -6283,7 +6312,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>88</v>
@@ -6304,19 +6333,19 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6335,16 +6364,16 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6394,7 +6423,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6409,7 +6438,7 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>80</v>
@@ -6418,12 +6447,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6449,10 +6478,10 @@
         <v>174</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6503,7 +6532,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6518,21 +6547,21 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6558,13 +6587,13 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6593,10 +6622,10 @@
         <v>197</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
@@ -6614,7 +6643,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6638,12 +6667,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6669,13 +6698,13 @@
         <v>193</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6701,13 +6730,13 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -6725,7 +6754,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6740,7 +6769,7 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>80</v>
@@ -6749,12 +6778,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6777,16 +6806,16 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6836,7 +6865,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6851,7 +6880,7 @@
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>80</v>
@@ -6861,6 +6890,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AM48">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI47">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
+++ b/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="382">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.3</t>
+    <t>0.1.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -469,28 +469,32 @@
     <t>The date or estimated date that the allergy or intolerance resolved. This is called abatement because of the many overloaded connotations associated with resolution.</t>
   </si>
   <si>
-    <t>Age is generally used when the patient reports an age at which the allergy or intolerance abated. If there is no abatement element, the clinicalStatus can be used to convey whether allergy or intolerance has resolved or not. When abatementString exists, it conveys that the allergy or intolerance is abated.</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.extension:abatement.id</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.extension.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
+    <t>Age is generally used when the patient reports an age at which the AllergyIntolerance was abated. Period is generally used to convey an imprecise abatement date that occurred within the time period. Range is generally used to convey an imprecise age range (e.g. 4 to 6 years old). If there is no abatement element, the clinicalStatus can be used to convey whether allergy or intolerance has resolved or not. When abatementString exists, it conveys that the allergy or intolerance is abated.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
+    <t>AllergyIntolerance.extension:abatement.id</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -540,7 +544,7 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t xml:space="preserve">type:$this}
@@ -550,10 +554,6 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">ext-1
-</t>
-  </si>
-  <si>
     <t>AllergyIntolerance.extension:abatement.value[x]:valueDateTime</t>
   </si>
   <si>
@@ -660,7 +660,7 @@
     <t>Assertion about certainty associated with the propensity, or potential risk, of a reaction to the identified substance (including pharmaceutical product).</t>
   </si>
   <si>
-    <t>The data type is CodeableConcept because verificationStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
+    <t>Import need to handle missing verificationStatus</t>
   </si>
   <si>
     <t>Assertion about certainty associated with a propensity, or potential risk, of a reaction to the identified substance.</t>
@@ -744,7 +744,7 @@
     <t>Estimate of the potential clinical harm, or seriousness, of the reaction to the identified substance.</t>
   </si>
   <si>
-    <t>The default criticality value for any propensity to an adverse reaction should be 'Low Risk', indicating at the very least a relative contraindication to deliberate or voluntary exposure to the substance. 'High Risk' is flagged if the clinician has identified a propensity for a more serious or potentially life-threatening reaction, such as anaphylaxis, and implies an absolute contraindication to deliberate or voluntary exposure to the substance. If this element is missing, the criticality is unknown (though it may be known elsewhere).  Systems that capture a severity at the condition level are actually representing the concept of criticality whereas the severity documented at the reaction level is representing the true reaction severity.  Existing systems that are capturing both condition criticality and reaction severity may use the term "severity" to represent both.  Criticality is the worst it could be in the future (i.e. situation-agnostic) whereas severity is situation-dependent.</t>
+    <t>Import need to handle missing criticality</t>
   </si>
   <si>
     <t>Estimate of the potential clinical harm, or seriousness, of a reaction to an identified substance.</t>
@@ -986,10 +986,6 @@
   </si>
   <si>
     <t>AllergyIntolerance.note.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>AllergyIntolerance.note.extension</t>
@@ -2682,7 +2678,7 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>139</v>
@@ -2699,10 +2695,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2725,13 +2721,13 @@
         <v>80</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>90</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2782,7 +2778,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2791,13 +2787,13 @@
         <v>88</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>151</v>
+        <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>80</v>
@@ -2808,10 +2804,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2882,7 +2878,7 @@
         <v>136</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>80</v>
@@ -2891,7 +2887,7 @@
         <v>137</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2917,10 +2913,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2946,13 +2942,13 @@
         <v>102</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2960,7 +2956,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>80</v>
@@ -3002,7 +2998,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>88</v>
@@ -3028,10 +3024,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3054,13 +3050,13 @@
         <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3099,7 +3095,7 @@
         <v>80</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
@@ -3109,7 +3105,7 @@
         <v>137</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3118,7 +3114,7 @@
         <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>100</v>
@@ -3138,7 +3134,7 @@
         <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>173</v>
@@ -3169,7 +3165,7 @@
         <v>175</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3220,7 +3216,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3229,7 +3225,7 @@
         <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>100</v>
@@ -3581,7 +3577,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>202</v>
       </c>
@@ -3594,13 +3590,13 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>89</v>
@@ -3927,7 +3923,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>88</v>
@@ -4380,7 +4376,7 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>262</v>
@@ -4425,7 +4421,7 @@
         <v>80</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
@@ -5153,13 +5149,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>307</v>
+        <v>149</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5210,7 +5206,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5225,7 +5221,7 @@
         <v>80</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>80</v>
@@ -5236,10 +5232,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5265,10 +5261,10 @@
         <v>133</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>180</v>
@@ -5312,7 +5308,7 @@
         <v>136</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>80</v>
@@ -5321,7 +5317,7 @@
         <v>137</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5336,7 +5332,7 @@
         <v>139</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>80</v>
@@ -5347,10 +5343,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5373,16 +5369,16 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5432,7 +5428,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5447,7 +5443,7 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>80</v>
@@ -5458,10 +5454,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5487,10 +5483,10 @@
         <v>174</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5541,7 +5537,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5556,7 +5552,7 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>80</v>
@@ -5567,10 +5563,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5593,13 +5589,13 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5650,7 +5646,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>88</v>
@@ -5665,7 +5661,7 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>80</v>
@@ -5676,10 +5672,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5702,13 +5698,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5759,7 +5755,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5774,7 +5770,7 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>80</v>
@@ -5785,10 +5781,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5811,13 +5807,13 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>307</v>
+        <v>149</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5868,7 +5864,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5883,7 +5879,7 @@
         <v>80</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>80</v>
@@ -5894,10 +5890,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5923,10 +5919,10 @@
         <v>133</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>180</v>
@@ -5979,7 +5975,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5994,7 +5990,7 @@
         <v>139</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>80</v>
@@ -6005,14 +6001,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6034,10 +6030,10 @@
         <v>133</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>180</v>
@@ -6092,7 +6088,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6118,10 +6114,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6147,13 +6143,13 @@
         <v>193</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6179,11 +6175,11 @@
         <v>80</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>80</v>
@@ -6201,7 +6197,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6216,7 +6212,7 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>80</v>
@@ -6227,14 +6223,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6256,13 +6252,13 @@
         <v>193</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6291,11 +6287,11 @@
         <v>112</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="Z43" t="s" s="2">
-        <v>354</v>
-      </c>
       <c r="AA43" t="s" s="2">
         <v>80</v>
       </c>
@@ -6312,7 +6308,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>88</v>
@@ -6333,19 +6329,19 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6364,16 +6360,16 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>307</v>
+        <v>149</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6423,7 +6419,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6438,7 +6434,7 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>80</v>
@@ -6449,10 +6445,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6478,10 +6474,10 @@
         <v>174</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6532,7 +6528,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6553,15 +6549,15 @@
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6587,13 +6583,13 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6622,11 +6618,11 @@
         <v>197</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>371</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
       </c>
@@ -6643,7 +6639,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6669,10 +6665,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6698,13 +6694,13 @@
         <v>193</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6730,14 +6726,14 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>377</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
       </c>
@@ -6754,7 +6750,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6769,7 +6765,7 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>80</v>
@@ -6780,10 +6776,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6809,13 +6805,13 @@
         <v>301</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6865,7 +6861,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>

--- a/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
+++ b/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.4</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
+++ b/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -1123,10 +1123,10 @@
     <t>Clinical symptoms/signs associated with the Event</t>
   </si>
   <si>
-    <t>Clinical symptoms and/or signs that are observed or associated with the adverse reaction event.</t>
-  </si>
-  <si>
-    <t>Manifestation can be expressed as a single word, phrase or brief description. For example: nausea, rash or no reaction. It is preferable that manifestation should be coded with a terminology, where possible. The values entered here may be used to display on an application screen as part of a list of adverse reactions, as recommended in the UK NHS CUI guidelines.  Terminologies commonly used include, but are not limited to, SNOMED CT or ICD10.</t>
+    <t>Hvilken reaksjon pasienten har hatt.</t>
+  </si>
+  <si>
+    <t>Helse-NIM anbefaler KJ 7497 (Reaksjonstype) for koding av manifestasjon.</t>
   </si>
   <si>
     <t>Type of allergy or intolerance reaction expected to be used in MyHealth@EU</t>
@@ -1175,7 +1175,7 @@
     <t>Reaction severity</t>
   </si>
   <si>
-    <t>Clinical assessment of the severity of the reaction event as a whole, potentially considering multiple different manifestations.</t>
+    <t>Hvor alvorlig reaksjon pasienten har hatt.</t>
   </si>
   <si>
     <t>It is acknowledged that this assessment is very subjective. There may be some specific practice domains where objective scales have been applied. Objective scales can be included in this model as extensions.</t>
@@ -5670,7 +5670,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>328</v>
       </c>
@@ -5689,7 +5689,7 @@
         <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>80</v>
@@ -6221,7 +6221,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>347</v>
       </c>
@@ -6240,7 +6240,7 @@
         <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>80</v>
@@ -6552,7 +6552,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>365</v>
       </c>
@@ -6571,7 +6571,7 @@
         <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>80</v>

--- a/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
+++ b/currentbuild/StructureDefinition-demo-at-allergy-intolerance.xlsx
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Dummy-tekst: Helse-NIM for overfølsomhet er en liste som inneholder informasjon om unormale reaksjoner, symptomer eller funn initiert av eksponering for en definert stimulus i en dose som normalt tolereres av andre. Informasjon om en pasients overfølsomhet er relevant i mange situasjoner, som ved vaksinasjon, kost på institusjon, rekvirering og utlevering av legemidler, herunder inkludert muligheten til å dele informasjon om en avkreftet overfølsomhet.</t>
+    <t>Demo-profil for registrering av allergi og intoleranse med utgangspunkt i HL7 EU Core og relevante norske føringer for overfølsomhet.</t>
   </si>
   <si>
     <t>Purpose</t>
